--- a/backend/data/attachments/risk_信用风险监测周报_1.xlsx
+++ b/backend/data/attachments/risk_信用风险监测周报_1.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trust-618</t>
+          <t>Trust-956</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>47437</v>
+        <v>42696</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,28 +464,28 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Trust-208</t>
+          <t>Trust-581</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33411</v>
+        <v>39010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -494,12 +494,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA-</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -511,11 +511,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Trust-280</t>
+          <t>Trust-750</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39193</v>
+        <v>37225</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -529,7 +529,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -541,11 +541,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Trust-430</t>
+          <t>Trust-428</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21088</v>
+        <v>48917</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -554,12 +554,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2024-06-14</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -571,11 +571,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Trust-683</t>
+          <t>Trust-395</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44998</v>
+        <v>48423</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -584,12 +584,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2025-01-16</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,25 +601,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Trust-286</t>
+          <t>Trust-358</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>36952</v>
+        <v>26186</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AA-</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2024-09-27</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -631,11 +631,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Trust-710</t>
+          <t>Trust-773</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23105</v>
+        <v>40559</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -644,47 +644,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2025-02-08</t>
+          <t>2024-01-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Trust-600</t>
+          <t>Trust-737</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41384</v>
+        <v>37669</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Normal</t>
         </is>
       </c>
     </row>
